--- a/output/pdf_financials_xlsx/APM.xlsx
+++ b/output/pdf_financials_xlsx/APM.xlsx
@@ -18735,10 +18735,10 @@
         </is>
       </c>
       <c r="E288" s="5" t="n">
-        <v>0.010153</v>
+        <v>-0.010153</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.067929</v>
+        <v>-0.067929</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/APM.xlsx
+++ b/output/pdf_financials_xlsx/APM.xlsx
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.09139799999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.27917</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>87.276</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.09139799999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.27917</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>87.276</v>
@@ -3975,10 +3975,10 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.223</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>-7.799</v>
@@ -4003,10 +4003,10 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.223</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>-7.799</v>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
@@ -13245,7 +13245,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/APM.xlsx
+++ b/output/pdf_financials_xlsx/APM.xlsx
@@ -1610,13 +1610,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.601</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>1.285</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="41">
@@ -1638,13 +1638,13 @@
         <v>0.198</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.888</v>
+        <v>1.489</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1.665</v>
+        <v>2.95</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1.957</v>
+        <v>2.547</v>
       </c>
     </row>
     <row r="42">
@@ -2382,19 +2382,19 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>4.224</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>4.288</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>5.177</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>3.318</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="68">
@@ -3729,13 +3729,13 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="116">
@@ -9694,7 +9694,11 @@
           <t>Net income (loss) $ 118,159 $</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -10641,7 +10645,11 @@
           <t>Proceeds from disposal of marketable securities 5 48,170</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -11302,7 +11310,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -12384,7 +12396,11 @@
           <t>Proceeds from disposal of marketable securities 6</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -13998,7 +14014,11 @@
           <t>Deferred income taxes expense 15</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -15538,7 +15558,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E225" s="5" t="n">
         <v>0.1035</v>
       </c>
@@ -18223,7 +18247,11 @@
           <t>Deferred income tax recovery (expense) 17</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
